--- a/VerveStacks_TJK_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_TJK_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TJK_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2A8919F-4A25-4B15-872C-AF50E22A7D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{52A31F38-6CB3-45D4-832F-2D0BFE29732B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0AB8EECA-D334-439B-B7E9-C95DC1484A10}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{69EA4DE9-B564-4BCF-9100-FF292EB97E00}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -550,7 +550,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BA3E23E-8EDB-4540-8B0D-4F2C11414BFC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0512ABB5-AF33-49E4-83FA-B046CB059B1D}">
   <dimension ref="B3:L15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_TJK_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_TJK_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TJK_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{52A31F38-6CB3-45D4-832F-2D0BFE29732B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{38503825-D50E-427F-8FEB-A55257790E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{69EA4DE9-B564-4BCF-9100-FF292EB97E00}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A1A93360-D220-4679-8A94-175D560F64FC}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -550,7 +550,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0512ABB5-AF33-49E4-83FA-B046CB059B1D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00FC0357-71A6-4C0F-B350-82E37CF45C6D}">
   <dimension ref="B3:L15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_TJK_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_TJK_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TJK_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{38503825-D50E-427F-8FEB-A55257790E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9C31485-242A-460A-93D3-61AC228A0D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A1A93360-D220-4679-8A94-175D560F64FC}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3271A459-B3FF-4CC8-A670-98BA5FFFE5BD}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -550,7 +550,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00FC0357-71A6-4C0F-B350-82E37CF45C6D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07ADE894-DF57-4CDF-A5EA-B6B5F9EA2894}">
   <dimension ref="B3:L15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_TJK_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_TJK_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TJK_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9C31485-242A-460A-93D3-61AC228A0D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{401CEDD2-DF4B-4B09-9D2A-B7AADEBD4463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3271A459-B3FF-4CC8-A670-98BA5FFFE5BD}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D20BA5AC-25AC-4391-862F-0C0EA1C57C20}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -550,7 +550,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07ADE894-DF57-4CDF-A5EA-B6B5F9EA2894}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF1CA378-DAD2-43DD-A821-B52AF2B36E3A}">
   <dimension ref="B3:L15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
